--- a/Progress Report.xlsx
+++ b/Progress Report.xlsx
@@ -216,7 +216,7 @@
       </c>
       <c r="C1" s="2" t="str">
         <f>CONCATENATE(COUNTIF($A$4:$A$51,TRUE), "/", COUNTA($C$4:$C$51), " 完成  ")</f>
-        <v>1/3 完成  </v>
+        <v>2/3 完成  </v>
       </c>
     </row>
     <row r="2" ht="6.0" customHeight="1">
@@ -248,7 +248,7 @@
     </row>
     <row r="5" ht="26.25" customHeight="1">
       <c r="A5" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>6</v>
